--- a/data.xlsx
+++ b/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{300DE337-3D45-4F0C-A579-1C389B31F715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9C9543-C9A7-4565-B179-2ADA18B7DA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2016" yWindow="2520" windowWidth="26160" windowHeight="14592" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
+    <workbookView xWindow="7716" yWindow="2520" windowWidth="20460" windowHeight="14592" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
   <sheets>
     <sheet name="deepseek_csv_20260722_b23856" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="134">
   <si>
     <t>name</t>
   </si>
@@ -37,380 +37,412 @@
     <t>style</t>
   </si>
   <si>
+    <t>https://space.bilibili.com/3493292593383796</t>
+  </si>
+  <si>
+    <t>0.png</t>
+  </si>
+  <si>
+    <t>华立电竞</t>
+  </si>
+  <si>
+    <t>https://space.bilibili.com/332563726</t>
+  </si>
+  <si>
+    <t>wec.png</t>
+  </si>
+  <si>
+    <t>https://wikiwiki.jp/taiko-fumen/</t>
+  </si>
+  <si>
+    <t>日本玩家搭建的wiki，数据全面历史悠久</t>
+  </si>
+  <si>
+    <t>wiki.png</t>
+  </si>
+  <si>
+    <t>韩国玩家搭建的wiki，数据全面历史悠久</t>
+  </si>
+  <si>
+    <t>wiki_ko.png</t>
+  </si>
+  <si>
+    <t>https://taiko.fandom.com/zh/wiki/%E9%A6%96%E9%A0%81</t>
+  </si>
+  <si>
+    <t>音游地图</t>
+  </si>
+  <si>
+    <t>https://map.bemanicn.com/games/31</t>
+  </si>
+  <si>
+    <t>bemani.png</t>
+  </si>
+  <si>
+    <t>https://qun.qq.com/universal-share/share?ac=1&amp;authKey=IT7nCJLnewnitCHF61dxFUr2oVgR%2F6L0Chf7hIVAbh2sds16Br9%2B9CJssWnQiJO%2B&amp;busi_data=eyJncm91cENvZGUiOiIyOTAxODQxNDciLCJ0b2tlbiI6InJ3aHBJV1dLT0VYeHZjejVDRTllUFNpbTd3WHFYaWxGa1FMMzR4QWl4U3I4ZTVva21jRms5UnhUSzErRVhaSTgiLCJ1aW4iOiIzMzkyOTA2NDAifQ%3D%3D&amp;data=yDKLKd-Pa1L25EwAck6iQn-SH2deyWEvvRAbjzZj91vQaobsQJsvUMI8ADHoc7F2LbTNINM7_16YNwHgkWoNJg&amp;svctype=4&amp;tempid=h5_group_info</t>
+  </si>
+  <si>
+    <t>葉月ゆら主页</t>
+  </si>
+  <si>
+    <t>https://hatukiyura.sakura.ne.jp/</t>
+  </si>
+  <si>
+    <t>叶月由罗的个人主页，可以查询到其往年作品和活动日程</t>
+  </si>
+  <si>
+    <t>yura.jpg</t>
+  </si>
+  <si>
+    <t>Rating系统</t>
+  </si>
+  <si>
+    <t>https://v2.rating.ourtaiko.org/v2test</t>
+  </si>
+  <si>
+    <t>国内玩家开发的成绩评分系统</t>
+  </si>
+  <si>
+    <t>https://fumen-database.com/difficulty/?const_desc</t>
+  </si>
+  <si>
+    <t>Donder查分器</t>
+  </si>
+  <si>
+    <t>https://prober.ourtaiko.org/search</t>
+  </si>
+  <si>
+    <t>luluxia.png</t>
+  </si>
+  <si>
+    <t>DonderNote</t>
+  </si>
+  <si>
+    <t>https://hatahata.outsystemscloud.com/DonderNote/Menu</t>
+  </si>
+  <si>
+    <t>DonderNote.png</t>
+  </si>
+  <si>
+    <t>TaikoNauts</t>
+  </si>
+  <si>
+    <t>https://seesaawiki.jp/taikonauts/</t>
+  </si>
+  <si>
+    <t>TaikoNauts.ico</t>
+  </si>
+  <si>
+    <t>OpenTaiko</t>
+  </si>
+  <si>
+    <t>https://opentaiko.github.io/</t>
+  </si>
+  <si>
+    <t>OpenTaiko.ico</t>
+  </si>
+  <si>
+    <t>ESE TJA</t>
+  </si>
+  <si>
+    <t>https://ese.tjadataba.se/ESE/ESE/</t>
+  </si>
+  <si>
+    <t>ese.png</t>
+  </si>
+  <si>
+    <t>ESE Helper</t>
+  </si>
+  <si>
+    <t>https://taiko.vanillaaaa.org/</t>
+  </si>
+  <si>
+    <t>https://wwaya.lanzoup.com/iHj8b3e7ooyh</t>
+  </si>
+  <si>
+    <t>可视化的谱面编辑，让小白也能迅速创建自己的太鼓谱面</t>
+  </si>
+  <si>
+    <t>PeepoDrumKit.ico</t>
+  </si>
+  <si>
+    <t>TaikoWeb</t>
+  </si>
+  <si>
+    <t>https://taiko.asia/</t>
+  </si>
+  <si>
+    <t>太鼓达人在线模拟器</t>
+  </si>
+  <si>
+    <t>taikoweb.png</t>
+  </si>
+  <si>
+    <t>歌曲检索器</t>
+  </si>
+  <si>
+    <t>https://olaf5103.cn:765/taiko/songs</t>
+  </si>
+  <si>
+    <t>Donder Asistant</t>
+  </si>
+  <si>
+    <t>https://dafrok.github.io/donder-assistant/analysis</t>
+  </si>
+  <si>
+    <t>Tja-Tools</t>
+  </si>
+  <si>
+    <t>https://whmhammer.github.io/tja-tools/</t>
+  </si>
+  <si>
+    <t>可以将tja文件转化为静态谱面图</t>
+  </si>
+  <si>
+    <t>Tja Analyser</t>
+  </si>
+  <si>
+    <t>https://tjaanalyzer-ja.ckq.me/</t>
+  </si>
+  <si>
+    <t>TaikoImager</t>
+  </si>
+  <si>
+    <t>可以获得还原官方视觉效果的谱面片段或谱面图，支持各种演奏选项</t>
+  </si>
+  <si>
+    <t>AI定数预测</t>
+  </si>
+  <si>
+    <t>https://tjapre.haxif.com/</t>
+  </si>
+  <si>
+    <t>让AI对你创作的谱面进行难度的初步评估</t>
+  </si>
+  <si>
+    <t>kokoko.jpg</t>
+  </si>
+  <si>
+    <t>菌菌控制台</t>
+  </si>
+  <si>
+    <t>https://kinoko.zorua.cn/</t>
+  </si>
+  <si>
+    <t>菌菌控制台！可以管理自己的成绩以及使用菌菌的多项隐藏功能！</t>
+  </si>
+  <si>
+    <t>junjun.png</t>
+  </si>
+  <si>
+    <t>菌菌别名表格</t>
+  </si>
+  <si>
+    <t>https://www.kdocs.cn/l/cauSVZId2ohu</t>
+  </si>
+  <si>
+    <t>Sakura Bot</t>
+  </si>
+  <si>
+    <t>https://viewer.sakura-bot.cn/</t>
+  </si>
+  <si>
+    <t>猫鼓的小店</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.8ceeLYiw0FAY9K7</t>
+  </si>
+  <si>
+    <t>cat.png</t>
+  </si>
+  <si>
+    <t>Power的小店</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.8Yfnk26SrA8pUqZ</t>
+  </si>
+  <si>
+    <t>power.png</t>
+  </si>
+  <si>
+    <t>鱼鼓的小店</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.81neAPV?tk=6DKIgHaFqR5</t>
+  </si>
+  <si>
+    <t>sakataiko.png</t>
+  </si>
+  <si>
+    <t>神童同学</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.8cJNqUO?tk=jmmEgH1Qo0i</t>
+  </si>
+  <si>
+    <t>stg.png</t>
+  </si>
+  <si>
+    <t>伪都特产私棍</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.81OScrk19TUpuPM</t>
+  </si>
+  <si>
+    <t>otto.png</t>
+  </si>
+  <si>
+    <t>单手全连逆战</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.8cqwDXa?tk=hurZgHYHZl1</t>
+  </si>
+  <si>
+    <t>nizhan.png</t>
+  </si>
+  <si>
+    <t>狂澜怒涛</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.8cqx9ES?tk=zVYNgHYHAvf</t>
+  </si>
+  <si>
+    <t>7f7f.png</t>
+  </si>
+  <si>
+    <t>西瓜的音游小铺</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.8Ys9Atv?tk=ZPbKgHYti3K</t>
+  </si>
+  <si>
+    <t>watermelon.png</t>
+  </si>
+  <si>
+    <t>ZDR</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.8210xIi?tk=yD8tgHYztMN</t>
+  </si>
+  <si>
+    <t>zdr.png</t>
+  </si>
+  <si>
+    <t>活体搁浅</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.81pdJXR?tk=0WqugHYwWq5</t>
+  </si>
+  <si>
+    <t>wai.jpg</t>
+  </si>
+  <si>
+    <t>不灭的灯</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.81pYYTI?tk=qfzFgHYu00f</t>
+  </si>
+  <si>
+    <t>deng.png</t>
+  </si>
+  <si>
+    <t>小言罐头</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.82YviOa?tk=oo9hgHYtJGQ</t>
+  </si>
+  <si>
+    <t>yan.png</t>
+  </si>
+  <si>
+    <t>哈基缘</t>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.8217LAp?tk=rOm4gH16WJD</t>
+  </si>
+  <si>
+    <t>yuan.png</t>
+  </si>
+  <si>
+    <t>小章木工坊</t>
+  </si>
+  <si>
+    <t>https://mobile.yangkeduo.com/mall_page.html?ps=IpGOWhdEwr</t>
+  </si>
+  <si>
+    <t>pdd.png</t>
+  </si>
+  <si>
+    <t>铭盛科技</t>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.8XcgB01nntTZ3dL?tk=AyHygHkEYP4</t>
+  </si>
+  <si>
+    <t>mingsheng.png</t>
+  </si>
+  <si>
     <t>太鼓之达人官方</t>
-  </si>
-  <si>
-    <t>https://space.bilibili.com/3493292593383796</t>
-  </si>
-  <si>
-    <t>0.png</t>
-  </si>
-  <si>
-    <t>华立电竞</t>
-  </si>
-  <si>
-    <t>https://space.bilibili.com/332563726</t>
-  </si>
-  <si>
-    <t>wec.png</t>
-  </si>
-  <si>
-    <t>太鼓WIKI（日）</t>
-  </si>
-  <si>
-    <t>https://wikiwiki.jp/taiko-fumen/</t>
-  </si>
-  <si>
-    <t>日本玩家搭建的wiki，数据全面历史悠久</t>
-  </si>
-  <si>
-    <t>wiki.png</t>
-  </si>
-  <si>
-    <t>太鼓WIKI（韩）</t>
-  </si>
-  <si>
-    <t>韩国玩家搭建的wiki，数据全面历史悠久</t>
-  </si>
-  <si>
-    <t>wiki_ko.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓之达人官方Bilibili账号</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>华立电竞官方Bilibili账号</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>太鼓Fandom</t>
-  </si>
-  <si>
-    <t>https://taiko.fandom.com/zh/wiki/%E9%A6%96%E9%A0%81</t>
-  </si>
-  <si>
-    <t>音游地图</t>
-  </si>
-  <si>
-    <t>https://map.bemanicn.com/games/31</t>
-  </si>
-  <si>
-    <t>bemani.png</t>
-  </si>
-  <si>
-    <t>太鼓达人全国群</t>
-  </si>
-  <si>
-    <t>https://qun.qq.com/universal-share/share?ac=1&amp;authKey=IT7nCJLnewnitCHF61dxFUr2oVgR%2F6L0Chf7hIVAbh2sds16Br9%2B9CJssWnQiJO%2B&amp;busi_data=eyJncm91cENvZGUiOiIyOTAxODQxNDciLCJ0b2tlbiI6InJ3aHBJV1dLT0VYeHZjejVDRTllUFNpbTd3WHFYaWxGa1FMMzR4QWl4U3I4ZTVva21jRms5UnhUSzErRVhaSTgiLCJ1aW4iOiIzMzkyOTA2NDAifQ%3D%3D&amp;data=yDKLKd-Pa1L25EwAck6iQn-SH2deyWEvvRAbjzZj91vQaobsQJsvUMI8ADHoc7F2LbTNINM7_16YNwHgkWoNJg&amp;svctype=4&amp;tempid=h5_group_info</t>
-  </si>
-  <si>
-    <t>葉月ゆら主页</t>
-  </si>
-  <si>
-    <t>https://hatukiyura.sakura.ne.jp/</t>
-  </si>
-  <si>
-    <t>叶月由罗的个人主页，可以查询到其往年作品和活动日程</t>
-  </si>
-  <si>
-    <t>yura.jpg</t>
-  </si>
-  <si>
-    <t>Rating系统</t>
-  </si>
-  <si>
-    <t>https://v2.rating.ourtaiko.org/v2test</t>
-  </si>
-  <si>
-    <t>国内玩家开发的成绩评分系统</t>
-  </si>
-  <si>
-    <t>Database定数表</t>
-  </si>
-  <si>
-    <t>https://fumen-database.com/difficulty/?const_desc</t>
-  </si>
-  <si>
-    <t>Donder查分器</t>
-  </si>
-  <si>
-    <t>https://prober.ourtaiko.org/search</t>
-  </si>
-  <si>
-    <t>luluxia.png</t>
-  </si>
-  <si>
-    <t>DonderNote</t>
-  </si>
-  <si>
-    <t>https://hatahata.outsystemscloud.com/DonderNote/Menu</t>
-  </si>
-  <si>
-    <t>DonderNote.png</t>
-  </si>
-  <si>
-    <t>TaikoNauts</t>
-  </si>
-  <si>
-    <t>https://seesaawiki.jp/taikonauts/</t>
-  </si>
-  <si>
-    <t>TaikoNauts.ico</t>
-  </si>
-  <si>
-    <t>OpenTaiko</t>
-  </si>
-  <si>
-    <t>https://opentaiko.github.io/</t>
-  </si>
-  <si>
-    <t>OpenTaiko.ico</t>
-  </si>
-  <si>
-    <t>ESE TJA</t>
-  </si>
-  <si>
-    <t>https://ese.tjadataba.se/ESE/ESE/</t>
-  </si>
-  <si>
-    <t>ese.png</t>
-  </si>
-  <si>
-    <t>ESE Helper</t>
-  </si>
-  <si>
-    <t>https://taiko.vanillaaaa.org/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国玩家群</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>全国范围的2000人玩家交流群</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓WIKI 日</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>太鼓WIKI 韩</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
     <t>PeepoDrumKit</t>
-  </si>
-  <si>
-    <t>https://wwaya.lanzoup.com/iHj8b3e7ooyh</t>
-  </si>
-  <si>
-    <t>可视化的谱面编辑，让小白也能迅速创建自己的太鼓谱面</t>
-  </si>
-  <si>
-    <t>PeepoDrumKit.ico</t>
-  </si>
-  <si>
-    <t>TaikoWeb</t>
-  </si>
-  <si>
-    <t>https://taiko.asia/</t>
-  </si>
-  <si>
-    <t>太鼓达人在线模拟器</t>
-  </si>
-  <si>
-    <t>taikoweb.png</t>
-  </si>
-  <si>
-    <t>歌曲检索器</t>
-  </si>
-  <si>
-    <t>https://olaf5103.cn:765/taiko/songs</t>
-  </si>
-  <si>
-    <t>Donder Asistant</t>
-  </si>
-  <si>
-    <t>https://dafrok.github.io/donder-assistant/analysis</t>
-  </si>
-  <si>
-    <t>Tja-Tools</t>
-  </si>
-  <si>
-    <t>https://whmhammer.github.io/tja-tools/</t>
-  </si>
-  <si>
-    <t>可以将tja文件转化为静态谱面图</t>
-  </si>
-  <si>
-    <t>Tja Analyser</t>
-  </si>
-  <si>
-    <t>https://tjaanalyzer-ja.ckq.me/</t>
-  </si>
-  <si>
-    <t>TaikoImager</t>
-  </si>
-  <si>
-    <t>https://doveonz.github.io/Taiko-no-Tatsujin-Imager/</t>
-  </si>
-  <si>
-    <t>可以获得还原官方视觉效果的谱面片段或谱面图，支持各种演奏选项</t>
-  </si>
-  <si>
-    <t>AI定数预测</t>
-  </si>
-  <si>
-    <t>https://tjapre.haxif.com/</t>
-  </si>
-  <si>
-    <t>让AI对你创作的谱面进行难度的初步评估</t>
-  </si>
-  <si>
-    <t>kokoko.jpg</t>
-  </si>
-  <si>
-    <t>菌菌控制台</t>
-  </si>
-  <si>
-    <t>https://kinoko.zorua.cn/</t>
-  </si>
-  <si>
-    <t>菌菌控制台！可以管理自己的成绩以及使用菌菌的多项隐藏功能！</t>
-  </si>
-  <si>
-    <t>junjun.png</t>
-  </si>
-  <si>
-    <t>菌菌别名表格</t>
-  </si>
-  <si>
-    <t>https://www.kdocs.cn/l/cauSVZId2ohu</t>
-  </si>
-  <si>
-    <t>Sakura Bot</t>
-  </si>
-  <si>
-    <t>https://viewer.sakura-bot.cn/</t>
-  </si>
-  <si>
-    <t>猫鼓的小店</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8ceeLYiw0FAY9K7</t>
-  </si>
-  <si>
-    <t>cat.png</t>
-  </si>
-  <si>
-    <t>Power的小店</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8Yfnk26SrA8pUqZ</t>
-  </si>
-  <si>
-    <t>power.png</t>
-  </si>
-  <si>
-    <t>鱼鼓的小店</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.81neAPV?tk=6DKIgHaFqR5</t>
-  </si>
-  <si>
-    <t>sakataiko.png</t>
-  </si>
-  <si>
-    <t>神童同学</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8cJNqUO?tk=jmmEgH1Qo0i</t>
-  </si>
-  <si>
-    <t>stg.png</t>
-  </si>
-  <si>
-    <t>伪都特产私棍</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.81OScrk19TUpuPM</t>
-  </si>
-  <si>
-    <t>otto.png</t>
-  </si>
-  <si>
-    <t>单手全连逆战</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8cqwDXa?tk=hurZgHYHZl1</t>
-  </si>
-  <si>
-    <t>nizhan.png</t>
-  </si>
-  <si>
-    <t>狂澜怒涛</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8cqx9ES?tk=zVYNgHYHAvf</t>
-  </si>
-  <si>
-    <t>7f7f.png</t>
-  </si>
-  <si>
-    <t>西瓜的音游小铺</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8Ys9Atv?tk=ZPbKgHYti3K</t>
-  </si>
-  <si>
-    <t>watermelon.png</t>
-  </si>
-  <si>
-    <t>ZDR</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8210xIi?tk=yD8tgHYztMN</t>
-  </si>
-  <si>
-    <t>zdr.png</t>
-  </si>
-  <si>
-    <t>活体搁浅</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.81pdJXR?tk=0WqugHYwWq5</t>
-  </si>
-  <si>
-    <t>wai.jpg</t>
-  </si>
-  <si>
-    <t>不灭的灯</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.81pYYTI?tk=qfzFgHYu00f</t>
-  </si>
-  <si>
-    <t>deng.png</t>
-  </si>
-  <si>
-    <t>小言罐头</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.82YviOa?tk=oo9hgHYtJGQ</t>
-  </si>
-  <si>
-    <t>yan.png</t>
-  </si>
-  <si>
-    <t>哈基缘</t>
-  </si>
-  <si>
-    <t>https://m.tb.cn/h.8217LAp?tk=rOm4gH16WJD</t>
-  </si>
-  <si>
-    <t>yuan.png</t>
-  </si>
-  <si>
-    <t>小章木工坊</t>
-  </si>
-  <si>
-    <t>https://mobile.yangkeduo.com/mall_page.html?ps=IpGOWhdEwr</t>
-  </si>
-  <si>
-    <t>pdd.png</t>
-  </si>
-  <si>
-    <t>铭盛科技</t>
-  </si>
-  <si>
-    <t>https://e.tb.cn/h.8XcgB01nntTZ3dL?tk=AyHygHkEYP4</t>
-  </si>
-  <si>
-    <t>mingsheng.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Database定数</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>华立官方淘汰的次品官机配件，可以尝试抽奖</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>20元以内性价比首选，建议选圆头枫木，自己购置手胶</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>为歌曲添加别名用于菌菌的歌曲查询</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://imager.donders.work</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -552,6 +584,14 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -850,7 +890,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -977,13 +1017,19 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - 着色 1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - 着色 2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - 着色 3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1009,6 +1055,7 @@
     <cellStyle name="标题 4" xfId="5" builtinId="19" customBuiltin="1"/>
     <cellStyle name="差" xfId="7" builtinId="27" customBuiltin="1"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="42" builtinId="8"/>
     <cellStyle name="好" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="汇总" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="计算" xfId="11" builtinId="22" customBuiltin="1"/>
@@ -1385,13 +1432,16 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
+      <c r="C2" t="s">
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -1399,13 +1449,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" t="s">
         <v>9</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -1413,16 +1466,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -1430,16 +1483,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1447,13 +1500,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -1461,13 +1514,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -1475,13 +1528,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1489,16 +1545,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -1506,16 +1562,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>2</v>
@@ -1523,13 +1579,13 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D11" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E11">
         <v>2</v>
@@ -1537,13 +1593,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D12" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1551,13 +1607,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1565,13 +1621,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1579,13 +1635,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1593,13 +1649,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D16" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1607,13 +1663,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1621,16 +1677,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D18" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1638,16 +1694,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1655,13 +1711,13 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>4</v>
@@ -1669,13 +1725,13 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>4</v>
@@ -1683,16 +1739,16 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B22" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C22" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>4</v>
@@ -1700,13 +1756,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23">
         <v>4</v>
@@ -1714,16 +1770,16 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
+        <v>61</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24">
         <v>4</v>
@@ -1731,16 +1787,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C25" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D25" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -1748,16 +1804,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D26" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -1765,13 +1821,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B27" t="s">
-        <v>80</v>
+        <v>72</v>
+      </c>
+      <c r="C27" t="s">
+        <v>132</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="E27">
         <v>5</v>
@@ -1779,13 +1838,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="D28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -1793,13 +1852,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B29" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="E29">
         <v>6</v>
@@ -1807,13 +1866,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E30">
         <v>6</v>
@@ -1821,13 +1880,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B31" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -1835,13 +1894,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -1849,13 +1908,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D33" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -1863,13 +1922,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="B34" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -1877,13 +1936,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B35" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D35" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -1891,13 +1950,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B36" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E36">
         <v>6</v>
@@ -1905,13 +1964,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="D37" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="E37">
         <v>6</v>
@@ -1919,13 +1978,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E38">
         <v>6</v>
@@ -1933,13 +1992,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D39" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="E39">
         <v>6</v>
@@ -1947,13 +2006,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D40" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E40">
         <v>6</v>
@@ -1961,13 +2020,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D41" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E41">
         <v>6</v>
@@ -1975,13 +2034,16 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>115</v>
+      </c>
+      <c r="C42" t="s">
+        <v>131</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -1989,13 +2051,16 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>118</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
       </c>
       <c r="D43" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -2003,6 +2068,9 @@
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B24" r:id="rId1" xr:uid="{0814D534-9BBD-4FF2-91BF-D9D2FA195367}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9C9543-C9A7-4565-B179-2ADA18B7DA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F26063B-7BDA-47FB-BDE0-66A2556313AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7716" yWindow="2520" windowWidth="20460" windowHeight="14592" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
+    <workbookView xWindow="8004" yWindow="2316" windowWidth="20460" windowHeight="14592" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
   <sheets>
     <sheet name="deepseek_csv_20260722_b23856" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="143">
   <si>
     <t>name</t>
   </si>
@@ -435,6 +435,42 @@
   </si>
   <si>
     <t>https://imager.donders.work</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rating.haxif.com</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI Rating分析</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>让AI对你的成绩信息进行分析总结</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>kokoko.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>stv.png</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://stevetaikocon.stevexmh.net/</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>控制器调试辅助</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://m.tb.cn/h.84CuZpo?tk=wIPJgCL06NC</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>StevenXMH</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1404,7 +1440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2205B9E-1FE6-4EB7-B604-2CFC0207A242}">
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.5546875" customWidth="1"/>
@@ -1787,16 +1823,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B25" t="s">
-        <v>64</v>
-      </c>
-      <c r="C25" t="s">
-        <v>65</v>
+        <v>140</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="D25" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -1804,47 +1837,50 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" t="s">
-        <v>68</v>
+        <v>135</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>134</v>
       </c>
       <c r="C26" t="s">
-        <v>69</v>
+        <v>136</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>137</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>65</v>
       </c>
       <c r="D27" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E27">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="C28" t="s">
+        <v>69</v>
       </c>
       <c r="D28" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -1852,41 +1888,44 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="C29" t="s">
+        <v>132</v>
       </c>
       <c r="D29" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E29">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B31" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -1894,13 +1933,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D32" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -1908,13 +1947,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B33" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -1922,13 +1961,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>90</v>
-      </c>
-      <c r="B34" t="s">
-        <v>91</v>
+        <v>142</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="D34" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -1936,13 +1975,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B35" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -1950,13 +1989,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B36" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D36" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E36">
         <v>6</v>
@@ -1964,13 +2003,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B37" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D37" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E37">
         <v>6</v>
@@ -1978,13 +2017,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E38">
         <v>6</v>
@@ -1992,13 +2031,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E39">
         <v>6</v>
@@ -2006,13 +2045,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D40" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E40">
         <v>6</v>
@@ -2020,13 +2059,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D41" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E41">
         <v>6</v>
@@ -2034,16 +2073,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B42" t="s">
-        <v>115</v>
-      </c>
-      <c r="C42" t="s">
-        <v>131</v>
+        <v>106</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -2051,18 +2087,63 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>108</v>
+      </c>
+      <c r="B43" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>111</v>
+      </c>
+      <c r="B44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D44" t="s">
+        <v>113</v>
+      </c>
+      <c r="E44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45" t="s">
+        <v>116</v>
+      </c>
+      <c r="E45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>117</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B46" t="s">
         <v>118</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C46" t="s">
         <v>130</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D46" t="s">
         <v>119</v>
       </c>
-      <c r="E43">
+      <c r="E46">
         <v>6</v>
       </c>
     </row>
@@ -2070,6 +2151,9 @@
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B24" r:id="rId1" xr:uid="{0814D534-9BBD-4FF2-91BF-D9D2FA195367}"/>
+    <hyperlink ref="B26" r:id="rId2" xr:uid="{1C29CD7D-8195-4F43-BF25-3937379C553D}"/>
+    <hyperlink ref="B25" r:id="rId3" xr:uid="{C7DC1DD1-A540-4732-A529-6E4F4FC7E8F3}"/>
+    <hyperlink ref="B34" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F26063B-7BDA-47FB-BDE0-66A2556313AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C3160C-8290-47B5-B3C5-6F350B3CAE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8004" yWindow="2316" windowWidth="20460" windowHeight="14592" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
+    <workbookView xWindow="8352" yWindow="2664" windowWidth="20460" windowHeight="14592" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
   <sheets>
     <sheet name="deepseek_csv_20260722_b23856" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="143">
   <si>
     <t>name</t>
   </si>
@@ -450,10 +450,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>kokoko.png</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>stv.png</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -471,6 +467,10 @@
   </si>
   <si>
     <t>StevenXMH</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>kokoko.jpg</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -1846,7 +1846,7 @@
         <v>136</v>
       </c>
       <c r="D26" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="E26">
         <v>4</v>
@@ -1961,13 +1961,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E34">
         <v>6</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\TaikoNavigation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00C3160C-8290-47B5-B3C5-6F350B3CAE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FA74AA-6279-4269-8786-0CC6231D0DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8352" yWindow="2664" windowWidth="20460" windowHeight="14592" xr2:uid="{21938866-CF94-43A1-8F72-DCC95449F496}"/>
   </bookViews>
@@ -94,15 +94,6 @@
     <t>yura.jpg</t>
   </si>
   <si>
-    <t>Rating系统</t>
-  </si>
-  <si>
-    <t>https://v2.rating.ourtaiko.org/v2test</t>
-  </si>
-  <si>
-    <t>国内玩家开发的成绩评分系统</t>
-  </si>
-  <si>
     <t>https://fumen-database.com/difficulty/?const_desc</t>
   </si>
   <si>
@@ -471,6 +462,18 @@
   </si>
   <si>
     <t>kokoko.jpg</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://wiki.ourtaiko.org/songs</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>OurtaikoWiki</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>国内玩家开发的成绩评分系统及谱面查询</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -1468,13 +1471,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B2" t="s">
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -1491,7 +1494,7 @@
         <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
         <v>9</v>
@@ -1502,7 +1505,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -1519,7 +1522,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B5" t="s">
         <v>10</v>
@@ -1536,7 +1539,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
@@ -1564,13 +1567,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -1598,13 +1601,13 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
+        <v>141</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>142</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -1615,10 +1618,10 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>12</v>
@@ -1629,13 +1632,13 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1643,13 +1646,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <v>2</v>
@@ -1657,13 +1660,13 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E14">
         <v>3</v>
@@ -1671,13 +1674,13 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E15">
         <v>3</v>
@@ -1685,13 +1688,13 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E16">
         <v>3</v>
@@ -1699,13 +1702,13 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E17">
         <v>3</v>
@@ -1713,16 +1716,16 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D18" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E18">
         <v>3</v>
@@ -1730,16 +1733,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" t="s">
         <v>48</v>
-      </c>
-      <c r="B19" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" t="s">
-        <v>51</v>
       </c>
       <c r="E19">
         <v>3</v>
@@ -1747,10 +1750,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
@@ -1761,10 +1764,10 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
@@ -1775,13 +1778,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
@@ -1792,10 +1795,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
@@ -1806,13 +1809,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
@@ -1823,13 +1826,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E25">
         <v>4</v>
@@ -1837,16 +1840,16 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C26" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E26">
         <v>4</v>
@@ -1854,16 +1857,16 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" t="s">
+        <v>61</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
         <v>63</v>
-      </c>
-      <c r="B27" t="s">
-        <v>64</v>
-      </c>
-      <c r="C27" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" t="s">
-        <v>66</v>
       </c>
       <c r="E27">
         <v>4</v>
@@ -1871,16 +1874,16 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" t="s">
         <v>67</v>
-      </c>
-      <c r="B28" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" t="s">
-        <v>69</v>
-      </c>
-      <c r="D28" t="s">
-        <v>70</v>
       </c>
       <c r="E28">
         <v>5</v>
@@ -1888,16 +1891,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C29" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E29">
         <v>5</v>
@@ -1905,10 +1908,10 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B30" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D30" t="s">
         <v>6</v>
@@ -1919,13 +1922,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E31">
         <v>6</v>
@@ -1933,13 +1936,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E32">
         <v>6</v>
@@ -1947,13 +1950,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D33" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E33">
         <v>6</v>
@@ -1961,13 +1964,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D34" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E34">
         <v>6</v>
@@ -1975,13 +1978,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E35">
         <v>6</v>
@@ -1989,13 +1992,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E36">
         <v>6</v>
@@ -2003,13 +2006,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E37">
         <v>6</v>
@@ -2017,13 +2020,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E38">
         <v>6</v>
@@ -2031,13 +2034,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D39" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E39">
         <v>6</v>
@@ -2045,13 +2048,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D40" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E40">
         <v>6</v>
@@ -2059,13 +2062,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B41" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D41" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E41">
         <v>6</v>
@@ -2073,13 +2076,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E42">
         <v>6</v>
@@ -2087,13 +2090,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B43" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D43" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E43">
         <v>6</v>
@@ -2101,13 +2104,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B44" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D44" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E44">
         <v>6</v>
@@ -2115,16 +2118,16 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D45" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E45">
         <v>6</v>
@@ -2132,16 +2135,16 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B46" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C46" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D46" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E46">
         <v>6</v>
@@ -2154,6 +2157,7 @@
     <hyperlink ref="B26" r:id="rId2" xr:uid="{1C29CD7D-8195-4F43-BF25-3937379C553D}"/>
     <hyperlink ref="B25" r:id="rId3" xr:uid="{C7DC1DD1-A540-4732-A529-6E4F4FC7E8F3}"/>
     <hyperlink ref="B34" r:id="rId4" xr:uid="{CACBC6E3-169E-4706-B683-51554D0D68AD}"/>
+    <hyperlink ref="B10" r:id="rId5" xr:uid="{E4702D2D-6FCD-4B5B-9E81-602FCFEC045E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
